--- a/exemple-ePrescription/ig/StructureDefinition-fr-cda-imputabilite-effet-indesirable.xlsx
+++ b/exemple-ePrescription/ig/StructureDefinition-fr-cda-imputabilite-effet-indesirable.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T08:51:06+00:00</t>
+    <t>2026-05-06T11:50:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3709,7 +3709,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
         <v>156</v>
       </c>
@@ -3724,13 +3724,13 @@
         <v>62</v>
       </c>
       <c r="F25" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>74</v>
+        <v>141</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>74</v>
@@ -3812,7 +3812,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
         <v>160</v>
       </c>
@@ -3827,13 +3827,13 @@
         <v>161</v>
       </c>
       <c r="F26" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>74</v>
+        <v>141</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>74</v>
@@ -4121,7 +4121,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
         <v>174</v>
       </c>
@@ -4142,7 +4142,7 @@
         <v>75</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>74</v>
+        <v>141</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>74</v>
